--- a/pr01/Практика_1_вариант_14.xlsx
+++ b/pr01/Практика_1_вариант_14.xlsx
@@ -30,10 +30,10 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -42,7 +42,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D08E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009DC3E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5A6BD"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,14 +94,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -437,9 +487,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -447,12 +497,12 @@
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
-    <col width="5" customWidth="1" min="18" max="18"/>
-    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="2" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,82 +518,65 @@
       <c r="D1" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>сднф</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Карта Карно (значения F)</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>F = (¬a∧¬b∧¬c∧d) ∨ (¬a∧¬b∧c∧d) ∨ (¬a∧b∧¬c∧d) ∨ (¬a∧b∧c∧d) ∨ (a∧¬b∧¬c∧¬d) ∨ (a∧¬b∧c∧¬d) ∨ (a∧b∧¬c∧¬d) ∨ (a∧b∧c∧¬d)</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>AB/CD</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="S2" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>F = (¬a∧¬b∧¬c∧d) ∨ (¬a∧¬b∧c∧d) ∨ (¬a∧b∧¬c∧d) ∨ (¬a∧b∧c∧d) ∨ (a∧¬b∧¬c∧¬d) ∨ (a∧¬b∧c∧¬d) ∨ (a∧b∧¬c∧¬d) ∨ (a∧b∧c∧¬d)</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -559,69 +592,69 @@
       <c r="D3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>мкнф</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>F = (a ∨ d) ∧ (¬a ∨ ¬d)      [= a ⊕ d]</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="P3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>F = (a ∨ d) ∧ (¬a ∨ ¬d)      [= a ⊕ d]</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="P4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -637,41 +670,58 @@
       <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="n">
+      <c r="P6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -688,89 +738,72 @@
       <c r="D7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>Для СДНФ — объединение единиц</t>
-        </is>
+      <c r="A8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
+          <t>СДНФ: группы единиц (¬a∧d, a∧¬d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
           <t>AB/CD</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="P9" s="6" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="S9" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -786,59 +819,59 @@
       <c r="D10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="P10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="P11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -854,41 +887,58 @@
       <c r="D12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1" t="n">
+      <c r="P13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -905,54 +955,29 @@
       <c r="D14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>Для МКНФ — объединение нулей</t>
-        </is>
+      <c r="A15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>AB/CD</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="R15" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>МКНФ: группы нулей (a∨d, ¬a∨¬d)</t>
         </is>
       </c>
     </row>
@@ -969,123 +994,160 @@
       <c r="D16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>AB/CD</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="P16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>0</v>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="O17" s="4" t="inlineStr">
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="O18" s="6" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="P17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>F16=55AA</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5=0101</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="O20" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>5=0101</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A=1010</t>
-        </is>
+      <c r="P20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A=1010</t>
+          <t>F16=55AA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>5=0101</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5=0101</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A=1010</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A=1010</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>F2=0101010110101010</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="O8:S8"/>
+    <mergeCell ref="O15:S15"/>
+    <mergeCell ref="O1:S1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>